--- a/data/trans_dic/P62A$viudedad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 16,55</t>
+          <t>5,6; 17,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 26,16</t>
+          <t>4,22; 24,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 27,41</t>
+          <t>5,01; 30,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,8</t>
+          <t>2,58; 10,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,63</t>
+          <t>1,36; 8,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,67</t>
+          <t>1,78; 10,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,1</t>
+          <t>5,42; 12,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 20,6</t>
+          <t>7,96; 20,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,92</t>
+          <t>0,0; 34,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 28,93</t>
+          <t>5,3; 31,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,96</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 23,4</t>
+          <t>9,67; 24,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,53</t>
+          <t>1,55; 9,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,61</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,84</t>
+          <t>10,0; 19,16</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,28; 29,63</t>
+          <t>16,27; 29,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 34,96</t>
+          <t>3,39; 33,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 35,88</t>
+          <t>15,07; 36,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 23,38</t>
+          <t>2,64; 25,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 16,17</t>
+          <t>4,58; 16,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,67</t>
+          <t>0,52; 5,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,57</t>
+          <t>3,9; 10,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,44</t>
+          <t>0,56; 6,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 23,95</t>
+          <t>13,81; 23,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,73</t>
+          <t>12,31; 20,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 24,23</t>
+          <t>9,98; 23,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 24,21</t>
+          <t>9,55; 24,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,89</t>
+          <t>8,79; 19,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 14,08</t>
+          <t>0,97; 13,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,12</t>
+          <t>2,37; 5,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,35</t>
+          <t>2,29; 6,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,51</t>
+          <t>2,71; 6,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,91</t>
+          <t>3,47; 16,04</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,19; 22,55</t>
+          <t>11,22; 22,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 42,46</t>
+          <t>23,03; 41,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,53; 33,45</t>
+          <t>21,54; 33,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 24,63</t>
+          <t>13,26; 24,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 12,25</t>
+          <t>6,63; 12,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 24,29</t>
+          <t>12,46; 23,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 20,69</t>
+          <t>13,14; 20,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 12,61</t>
+          <t>6,86; 12,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,98</t>
+          <t>9,51; 14,81</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,41</t>
+          <t>0,0; 40,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 65,34</t>
+          <t>8,59; 67,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,37; 85,77</t>
+          <t>76,75; 85,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,0; 86,19</t>
+          <t>75,63; 85,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,06; 84,5</t>
+          <t>73,94; 84,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,69</t>
+          <t>1,07; 4,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,14; 83,85</t>
+          <t>73,72; 83,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71,32; 81,29</t>
+          <t>70,82; 81,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71,0; 82,07</t>
+          <t>71,52; 81,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,78</t>
+          <t>2,12; 6,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,84; 18,47</t>
+          <t>13,87; 18,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,97; 53,3</t>
+          <t>45,58; 53,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,77; 47,07</t>
+          <t>39,61; 47,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,11; 39,6</t>
+          <t>31,83; 39,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,58</t>
+          <t>3,17; 8,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,66; 24,27</t>
+          <t>19,39; 24,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,34; 22,5</t>
+          <t>18,35; 22,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,07</t>
+          <t>14,33; 18,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,99</t>
+          <t>6,85; 12,9</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de viudedad</t>
+          <t>Población que, al menos, percibe una pensión de viudedad (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2162</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5897; 17150</t>
+          <t>5802; 17877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1848; 10907</t>
+          <t>1758; 10365</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1846; 10208</t>
+          <t>1865; 11234</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5830</t>
+          <t>0; 5715</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1564; 6936</t>
+          <t>1654; 6978</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1799; 11114</t>
+          <t>1752; 11256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1903; 11445</t>
+          <t>1914; 10765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6018</t>
+          <t>0; 5505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8962; 21980</t>
+          <t>9098; 21440</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5589</t>
+          <t>0; 5104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2229</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8591; 22203</t>
+          <t>8577; 21600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6961</t>
+          <t>0; 8904</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1912; 10798</t>
+          <t>1979; 11623</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6534</t>
+          <t>0; 6562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5624; 14122</t>
+          <t>5839; 14782</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8792</t>
+          <t>0; 8134</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2107; 12645</t>
+          <t>2052; 12056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7635</t>
+          <t>0; 7248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16113; 31679</t>
+          <t>16813; 32212</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1830</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10247</t>
+          <t>0; 10250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21350; 38848</t>
+          <t>21335; 39005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>731; 7420</t>
+          <t>721; 7138</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7969; 21142</t>
+          <t>8880; 21434</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1694; 11474</t>
+          <t>1298; 12268</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2332; 8349</t>
+          <t>2363; 8528</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>726; 7913</t>
+          <t>730; 8316</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9454; 25800</t>
+          <t>9524; 26497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1262; 12133</t>
+          <t>1244; 13497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25146; 43765</t>
+          <t>25234; 42472</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1822</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4726</t>
+          <t>0; 5573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36756; 61191</t>
+          <t>36328; 59058</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11544; 27387</t>
+          <t>11275; 27038</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11635; 28042</t>
+          <t>11062; 28283</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11999; 30204</t>
+          <t>12703; 28887</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3598; 46666</t>
+          <t>3211; 46252</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11540; 29058</t>
+          <t>11253; 27943</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10734; 29575</t>
+          <t>10677; 29838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13027; 31897</t>
+          <t>13265; 31306</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21779; 99668</t>
+          <t>21752; 100523</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5595</t>
+          <t>0; 5701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1822</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15792; 31821</t>
+          <t>15836; 31791</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24441; 42951</t>
+          <t>23297; 42062</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48771; 75779</t>
+          <t>48808; 76169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26351; 50798</t>
+          <t>27337; 50033</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14744; 27134</t>
+          <t>14680; 27496</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23533; 44657</t>
+          <t>22916; 43216</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48767; 78472</t>
+          <t>49821; 78368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25881; 50422</t>
+          <t>27450; 51383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34056; 54295</t>
+          <t>34460; 53682</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4160</t>
+          <t>0; 4212</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>911; 7089</t>
+          <t>932; 7351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>208593; 234258</t>
+          <t>209624; 234646</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>204619; 232051</t>
+          <t>203614; 230824</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>184170; 210135</t>
+          <t>183877; 210595</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2155; 9198</t>
+          <t>2106; 8684</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>210138; 237650</t>
+          <t>208933; 237437</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>203498; 231932</t>
+          <t>202073; 232417</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182541; 211011</t>
+          <t>183881; 209913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4619; 14027</t>
+          <t>4392; 14383</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7620</t>
+          <t>0; 6735</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 11342</t>
+          <t>0; 12303</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5602</t>
+          <t>0; 5228</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109315; 145811</t>
+          <t>109518; 147924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>259080; 307049</t>
+          <t>262575; 309304</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>296297; 350745</t>
+          <t>295144; 351803</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>235866; 290898</t>
+          <t>233771; 292338</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29897; 79405</t>
+          <t>29316; 79793</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>257933; 318400</t>
+          <t>254451; 315671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>296090; 363229</t>
+          <t>296262; 362176</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>234664; 295124</t>
+          <t>234033; 298690</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>121671; 222827</t>
+          <t>117463; 221125</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$viudedad-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$viudedad-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 17,26</t>
+          <t>5,32; 16,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,86</t>
+          <t>4,46; 25,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 30,17</t>
+          <t>5,15; 27,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,87</t>
+          <t>3,11; 11,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,74</t>
+          <t>1,35; 8,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,03</t>
+          <t>1,8; 10,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 12,78</t>
+          <t>5,4; 13,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 20,04</t>
+          <t>7,15; 19,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 31,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 31,14</t>
+          <t>5,53; 30,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,03</t>
+          <t>0,0; 18,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 24,49</t>
+          <t>9,58; 23,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 9,08</t>
+          <t>1,53; 9,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 19,16</t>
+          <t>9,6; 18,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 29,75</t>
+          <t>15,7; 28,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 33,63</t>
+          <t>3,44; 34,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 36,37</t>
+          <t>13,64; 36,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 25,0</t>
+          <t>3,35; 26,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 16,52</t>
+          <t>4,21; 15,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,96</t>
+          <t>0,54; 5,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,86</t>
+          <t>4,03; 10,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,06</t>
+          <t>0,55; 5,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 23,24</t>
+          <t>13,58; 23,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 20,01</t>
+          <t>11,83; 19,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 23,92</t>
+          <t>10,55; 23,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 24,42</t>
+          <t>9,42; 23,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 19,98</t>
+          <t>8,65; 20,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 13,96</t>
+          <t>8,06; 17,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,89</t>
+          <t>2,33; 6,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,41</t>
+          <t>2,25; 6,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,39</t>
+          <t>2,62; 6,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 16,04</t>
+          <t>11,65; 17,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,54 +1292,54 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 22,53</t>
+          <t>10,47; 21,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,03; 41,58</t>
+          <t>22,92; 41,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,54; 33,62</t>
+          <t>21,54; 33,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,26</t>
+          <t>13,22; 24,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,42</t>
+          <t>6,46; 12,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,46; 23,51</t>
+          <t>12,32; 23,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 20,66</t>
+          <t>12,82; 20,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,85</t>
+          <t>6,82; 12,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 14,81</t>
+          <t>8,83; 14,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,92</t>
+          <t>0,0; 40,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 67,75</t>
+          <t>7,77; 65,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,75; 85,91</t>
+          <t>76,33; 85,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,63; 85,74</t>
+          <t>75,39; 85,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>73,94; 84,69</t>
+          <t>73,76; 84,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,43</t>
+          <t>0,95; 4,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,72; 83,77</t>
+          <t>73,81; 83,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,82; 81,46</t>
+          <t>70,48; 81,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71,52; 81,64</t>
+          <t>71,0; 81,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,95</t>
+          <t>1,87; 6,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,87; 18,73</t>
+          <t>13,48; 17,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,58; 53,69</t>
+          <t>45,35; 53,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,61; 47,21</t>
+          <t>39,89; 47,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,83; 39,8</t>
+          <t>32,31; 40,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,62</t>
+          <t>6,64; 9,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,39; 24,06</t>
+          <t>19,55; 24,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 22,44</t>
+          <t>18,37; 22,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,33; 18,29</t>
+          <t>14,29; 18,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 12,9</t>
+          <t>10,58; 13,43</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>16388</t>
         </is>
       </c>
     </row>
@@ -1942,47 +1942,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5802; 17877</t>
+          <t>6219; 19023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1758; 10365</t>
+          <t>1861; 10618</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1865; 11234</t>
+          <t>1919; 10217</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5715</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1654; 6978</t>
+          <t>2259; 8599</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1752; 11256</t>
+          <t>1735; 10794</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1914; 10765</t>
+          <t>1928; 10769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5505</t>
+          <t>0; 5666</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9098; 21440</t>
+          <t>10243; 25229</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>25066</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5104</t>
+          <t>0; 6918</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8577; 21600</t>
+          <t>8342; 22679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 8904</t>
+          <t>0; 8128</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1979; 11623</t>
+          <t>2064; 11425</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6562</t>
+          <t>0; 6760</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5839; 14782</t>
+          <t>6570; 16331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8134</t>
+          <t>0; 7464</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2052; 12056</t>
+          <t>2037; 12314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7248</t>
+          <t>0; 7052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16813; 32212</t>
+          <t>17788; 34411</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>35688</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10250</t>
+          <t>0; 10415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,47 +2358,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21335; 39005</t>
+          <t>22519; 40307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>721; 7138</t>
+          <t>730; 7418</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8880; 21434</t>
+          <t>8035; 21505</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1298; 12268</t>
+          <t>1644; 13015</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2363; 8528</t>
+          <t>2388; 9020</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>730; 8316</t>
+          <t>748; 8297</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9524; 26497</t>
+          <t>9827; 26592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1244; 13497</t>
+          <t>1224; 12281</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25234; 42472</t>
+          <t>27177; 46794</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>49312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63318</t>
+          <t>65865</t>
         </is>
       </c>
     </row>
@@ -2561,52 +2561,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5573</t>
+          <t>0; 6110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36328; 59058</t>
+          <t>38053; 61982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11275; 27038</t>
+          <t>11921; 26951</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11062; 28283</t>
+          <t>10909; 27682</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12703; 28887</t>
+          <t>12500; 29710</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3211; 46252</t>
+          <t>11089; 23839</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11253; 27943</t>
+          <t>11039; 28725</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10677; 29838</t>
+          <t>10462; 29036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13265; 31306</t>
+          <t>12849; 32870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21752; 100523</t>
+          <t>53520; 81416</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43238</t>
+          <t>45413</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5701</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2774,54 +2774,54 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15836; 31791</t>
+          <t>15799; 31762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23297; 42062</t>
+          <t>23185; 41619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48808; 76169</t>
+          <t>48809; 75673</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27337; 50033</t>
+          <t>27259; 50139</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14680; 27496</t>
+          <t>15664; 29643</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22916; 43216</t>
+          <t>22647; 43777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49821; 78368</t>
+          <t>48605; 78754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27450; 51383</t>
+          <t>27259; 51732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34460; 53682</t>
+          <t>34724; 56104</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8213</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4212</t>
+          <t>0; 4162</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>932; 7351</t>
+          <t>810; 6778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>209624; 234646</t>
+          <t>208494; 234421</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>203614; 230824</t>
+          <t>202970; 230270</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>183877; 210595</t>
+          <t>183430; 210454</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2106; 8684</t>
+          <t>2012; 9480</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>208933; 237437</t>
+          <t>209201; 237381</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>202073; 232417</t>
+          <t>201094; 231356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>183881; 209913</t>
+          <t>182565; 210379</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4392; 14383</t>
+          <t>4148; 13935</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>58878</t>
+          <t>63757</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>196633</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6735</t>
+          <t>0; 6141</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 12303</t>
+          <t>0; 11316</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5228</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109518; 147924</t>
+          <t>115936; 154705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>262575; 309304</t>
+          <t>261261; 309755</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>295144; 351803</t>
+          <t>297225; 350528</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>233771; 292338</t>
+          <t>237298; 293879</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29316; 79793</t>
+          <t>52403; 76033</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>254451; 315671</t>
+          <t>256493; 316851</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>296262; 362176</t>
+          <t>296464; 359396</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>234033; 298690</t>
+          <t>233461; 298812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>117463; 221125</t>
+          <t>174574; 221484</t>
         </is>
       </c>
     </row>
